--- a/z_ai_mcdm/data-dummy/data_dummy_sertifikasi_dosen.xlsx
+++ b/z_ai_mcdm/data-dummy/data_dummy_sertifikasi_dosen.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laravel\IF3D-1-SIKOMPU\z_ai_mcdm\data-dummy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C754DA9E-8481-43AB-91AA-0CC2D8A342F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D95023EE-2E8C-49B9-AE44-80B13FFD08C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{67422809-CFEB-4B42-8660-B320DB9164A0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0B7D91E4-4668-40F3-A1FF-6F715457326E}"/>
   </bookViews>
   <sheets>
-    <sheet name="sertifikasi" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,14 +25,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="64">
-  <si>
-    <t>Data Dummy Sertifikasi Dosen</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+  <si>
+    <t>Nama_Dosen</t>
   </si>
   <si>
     <t>NIDN</t>
   </si>
   <si>
+    <t>prodi_asal</t>
+  </si>
+  <si>
+    <t>nama_sertifikat</t>
+  </si>
+  <si>
+    <t>institusi_pemberi</t>
+  </si>
+  <si>
+    <t>tahun_diperoleh</t>
+  </si>
+  <si>
+    <t>file_path</t>
+  </si>
+  <si>
+    <t>status_verifikasi</t>
+  </si>
+  <si>
     <t>Dosen 1</t>
   </si>
   <si>
@@ -42,6 +60,18 @@
     <t>IF</t>
   </si>
   <si>
+    <t>Web Development</t>
+  </si>
+  <si>
+    <t>BNSP</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100001.pdf</t>
+  </si>
+  <si>
+    <t>Diverifikasi</t>
+  </si>
+  <si>
     <t>Dosen 2</t>
   </si>
   <si>
@@ -51,12 +81,30 @@
     <t>TRPL</t>
   </si>
   <si>
+    <t>Machine Learning</t>
+  </si>
+  <si>
+    <t>Coursera</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100002.pdf</t>
+  </si>
+  <si>
     <t>Dosen 3</t>
   </si>
   <si>
     <t>100003</t>
   </si>
   <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>Cisco Academy</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100003.pdf</t>
+  </si>
+  <si>
     <t>Dosen 4</t>
   </si>
   <si>
@@ -66,6 +114,12 @@
     <t>AN</t>
   </si>
   <si>
+    <t>Software Engineering</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100004.pdf</t>
+  </si>
+  <si>
     <t>Dosen 5</t>
   </si>
   <si>
@@ -75,6 +129,15 @@
     <t>TP</t>
   </si>
   <si>
+    <t>IoT</t>
+  </si>
+  <si>
+    <t>Kampus Merdeka</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100005.pdf</t>
+  </si>
+  <si>
     <t>Dosen 6</t>
   </si>
   <si>
@@ -84,6 +147,15 @@
     <t>GM</t>
   </si>
   <si>
+    <t>Data Science</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100006.pdf</t>
+  </si>
+  <si>
+    <t>Tidak Valid</t>
+  </si>
+  <si>
     <t>Dosen 7</t>
   </si>
   <si>
@@ -93,12 +165,27 @@
     <t>TRM</t>
   </si>
   <si>
+    <t>Cyber Security</t>
+  </si>
+  <si>
+    <t>Udemy</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100007.pdf</t>
+  </si>
+  <si>
     <t>Dosen 8</t>
   </si>
   <si>
     <t>100008</t>
   </si>
   <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100008.pdf</t>
+  </si>
+  <si>
     <t>Dosen 9</t>
   </si>
   <si>
@@ -108,122 +195,32 @@
     <t>RKS</t>
   </si>
   <si>
+    <t>Cloud Computing</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>/uploads/sertifikat_100009.pdf</t>
+  </si>
+  <si>
     <t>Dosen 10</t>
   </si>
   <si>
     <t>100010</t>
   </si>
   <si>
-    <t xml:space="preserve">Nama </t>
-  </si>
-  <si>
-    <t>nama_sertifikat</t>
-  </si>
-  <si>
-    <t>institusi_pemberi</t>
-  </si>
-  <si>
-    <t>tahun_diperoleh</t>
-  </si>
-  <si>
-    <t>file_path</t>
-  </si>
-  <si>
-    <t>status_verifikasi</t>
-  </si>
-  <si>
-    <t>BNSP</t>
-  </si>
-  <si>
-    <t>Coursera</t>
-  </si>
-  <si>
-    <t>Cisco Academy</t>
-  </si>
-  <si>
-    <t>Kampus Merdeka</t>
-  </si>
-  <si>
-    <t>Udemy</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Web Development</t>
-  </si>
-  <si>
-    <t>Machine Learning</t>
-  </si>
-  <si>
-    <t>Networking</t>
-  </si>
-  <si>
-    <t>Software Engineering</t>
-  </si>
-  <si>
-    <t>IoT</t>
-  </si>
-  <si>
-    <t>Data Science</t>
-  </si>
-  <si>
-    <t>Cyber Security</t>
-  </si>
-  <si>
-    <t>Database</t>
-  </si>
-  <si>
-    <t>Cloud Computing</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100001.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100002.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100003.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100004.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100005.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100006.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100007.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100008.pdf</t>
-  </si>
-  <si>
-    <t>/uploads/sertifikat_100009.pdf</t>
-  </si>
-  <si>
     <t>/uploads/sertifikat_100010.pdf</t>
   </si>
   <si>
-    <t>Diverifikasi</t>
-  </si>
-  <si>
-    <t>Tidak Valid</t>
-  </si>
-  <si>
     <t>Menunggu</t>
-  </si>
-  <si>
-    <t>prodi_asal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,14 +242,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -268,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -291,34 +280,19 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -633,326 +607,297 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF438EE-B832-42D1-829B-72F1F9462365}">
-  <dimension ref="B2:I14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BCA7D8F-EDBE-473C-8FEA-447F94F55BD9}">
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" customWidth="1"/>
-    <col min="6" max="6" width="17.453125" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="17.54296875" customWidth="1"/>
-    <col min="9" max="9" width="21.54296875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2023</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2024</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2022</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2023</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2024</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="H7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2022</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2025</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="4">
         <v>2023</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="G10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="4">
-        <v>2022</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="4">
-        <v>2023</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="4">
-        <v>2023</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="4">
-        <v>2024</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="F11" s="4">
+        <v>2025</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="4">
-        <v>2022</v>
-      </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="4">
-        <v>2023</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2025</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="4" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>